--- a/public/CircuitBreakerCalculateSample.xlsx
+++ b/public/CircuitBreakerCalculateSample.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MILITARY HTTPX\WattWizard-backend\public\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\M\Downloads\ezzat\WattWizards\backend\public\samples\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A0E7056-FD26-40AA-8B9D-4F580F808612}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4920AF4B-35BA-42AF-806E-15EFC62B8B9D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10560" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,30 +26,24 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
-  <si>
-    <t>MachineNum</t>
-  </si>
-  <si>
-    <t>powerFactor</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
   <si>
     <t>Voltage</t>
   </si>
   <si>
-    <t>watt</t>
-  </si>
-  <si>
-    <t>WattUnit</t>
-  </si>
-  <si>
-    <t>phases</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HP </t>
-  </si>
-  <si>
-    <t xml:space="preserve">one phase </t>
+    <t>Machines number</t>
+  </si>
+  <si>
+    <t>Power</t>
+  </si>
+  <si>
+    <t>Power unit</t>
+  </si>
+  <si>
+    <t>Power factor</t>
+  </si>
+  <si>
+    <t>Phases</t>
   </si>
 </sst>
 </file>
@@ -398,43 +392,26 @@
   <sheetData>
     <row r="1" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C1" s="2" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>1</v>
       </c>
       <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A2" s="1">
-        <v>3</v>
-      </c>
-      <c r="B2" s="1">
-        <v>3</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D2" s="3">
-        <v>220</v>
-      </c>
-      <c r="E2" s="1">
-        <v>0.9</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>7</v>
-      </c>
+      <c r="D2" s="3"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.35">
       <c r="D3" s="3"/>
@@ -445,7 +422,7 @@
   </sheetData>
   <dataValidations count="2">
     <dataValidation type="list" showInputMessage="1" showErrorMessage="1" errorTitle="select valid power unit" sqref="C2:C1048576" xr:uid="{B0C10EFF-8489-46E5-AE1B-3089EBAB665C}">
-      <formula1>"W , KW , MW , HP , milliWatt"</formula1>
+      <formula1>"W , KW , MW , HP , milli watt"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="select valid phase unit" sqref="F2:F1048576" xr:uid="{97D1D839-88D5-4023-A072-DE6F1B704508}">
       <formula1>"one phase , three phases"</formula1>
